--- a/docs/downloads/经营分_津河省区__唐山北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__唐山北片区_2026-10-18.xlsx
@@ -1115,17 +1115,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7316515741600417842</t>
+          <t>7102768023395633189</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（唐山玉田店）</t>
+          <t>派酒店（唐山迁西北岸新区店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>白玉兰酒店(玉田店)</t>
+          <t>派酒店(唐山迁西北岸新区店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1137,7 +1137,7 @@
         <v>82</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -1163,7 +1163,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1203,17 +1203,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7418029787958282277</t>
+          <t>7316515741600417842</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>麗枫酒店（唐山中心医院店）</t>
+          <t>白玉兰商务酒店（唐山玉田店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>麗枫酒店(唐山中心医院店)</t>
+          <t>白玉兰酒店(玉田店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1225,7 +1225,7 @@
         <v>82</v>
       </c>
       <c r="I8" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
@@ -1251,7 +1251,7 @@
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6741041123524954123</t>
+          <t>7418029787958282277</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>希岸酒店唐山北站店</t>
+          <t>麗枫酒店（唐山中心医院店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>希岸酒店(唐山北站店)</t>
+          <t>麗枫酒店(唐山中心医院店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1372,20 +1372,24 @@
           <t>唐山北片区</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>唐山市</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601265040777545741</t>
+          <t>6741041123524954123</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>希岸酒店河北玉田店</t>
+          <t>希岸酒店唐山北站店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>希岸酒店(玉田店)</t>
+          <t>希岸酒店(唐山北站店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1417,13 +1421,13 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1456,24 +1460,20 @@
           <t>唐山北片区</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>唐山市</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7102768023395633189</t>
+          <t>6601265040777545741</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>派酒店（唐山迁西北岸新区店）</t>
+          <t>希岸酒店河北玉田店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>派酒店(唐山迁西北岸新区店)</t>
+          <t>希岸酒店(玉田店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1505,13 +1505,13 @@
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1727,33 +1727,33 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7405426591590828032</t>
+          <t>7277808830371596324</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>遵化燕山花园希岸Deluxe酒店</t>
+          <t>河北省唐山市迁安市燕山中路项目</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>遵化燕山花园希岸Deluxe酒店</t>
+          <t>白玉兰酒店(迁安燕山中路店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1763,19 +1763,19 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1815,33 +1815,33 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7277808830371596324</t>
+          <t>7405426591590828032</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>河北省唐山市迁安市燕山中路项目</t>
+          <t>遵化燕山花园希岸Deluxe酒店</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>白玉兰酒店(迁安燕山中路店)</t>
+          <t>遵化燕山花园希岸Deluxe酒店</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1851,13 +1851,13 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
